--- a/_Шаблон таблицы (для GPT).xlsx
+++ b/_Шаблон таблицы (для GPT).xlsx
@@ -8,6 +8,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="данные новые" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Пояснения" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -25,7 +26,7 @@
     <numFmt numFmtId="169" formatCode="#,##0.000"/>
     <numFmt numFmtId="170" formatCode="0.000"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <charset val="204"/>
@@ -133,6 +134,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -290,7 +295,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -460,6 +465,13 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1267,4 +1279,174 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="68" t="inlineStr">
+        <is>
+          <t>Пояснения к таблице: откуда взята каждая цифра</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="69" t="inlineStr">
+        <is>
+          <t>Заполняется автоматически вместе с таблицей. По каждой строке видно, из какого источника взято значение, в каких единицах и что важно учесть перед использованием в модели.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="71" t="inlineStr">
+        <is>
+          <t>Строка таблицы</t>
+        </is>
+      </c>
+      <c r="B4" s="71" t="inlineStr">
+        <is>
+          <t>Факт: откуда</t>
+        </is>
+      </c>
+      <c r="C4" s="71" t="inlineStr">
+        <is>
+          <t>Прогноз: откуда</t>
+        </is>
+      </c>
+      <c r="D4" s="71" t="inlineStr">
+        <is>
+          <t>Что именно за показатель</t>
+        </is>
+      </c>
+      <c r="E4" s="71" t="inlineStr">
+        <is>
+          <t>Единицы и пересчёты</t>
+        </is>
+      </c>
+      <c r="F4" s="71" t="inlineStr">
+        <is>
+          <t>Ограничения, на что смотреть</t>
+        </is>
+      </c>
+      <c r="G4" s="71" t="inlineStr">
+        <is>
+          <t>Дата получения (retrieved_at)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="72" t="inlineStr">
+        <is>
+          <t>Выручка, млн CNY</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="72" t="inlineStr">
+        <is>
+          <t>BVPS, CNY/акц.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="72" t="inlineStr">
+        <is>
+          <t>EPS diluted, CNY/акц.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="72" t="inlineStr">
+        <is>
+          <t>Дивиденд annual DPS, CNY/акц.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="72" t="inlineStr">
+        <is>
+          <t>Курс 1 CNY в HKD</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="73" t="inlineStr">
+        <is>
+          <t>Общие замечания</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="70" t="inlineStr">
+        <is>
+          <t>Тема</t>
+        </is>
+      </c>
+      <c r="B13" s="70" t="inlineStr">
+        <is>
+          <t>Пояснение</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="72" t="inlineStr">
+        <is>
+          <t>Финансовый год</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="72" t="inlineStr">
+        <is>
+          <t>Последняя фактическая точка</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="72" t="inlineStr">
+        <is>
+          <t>Выбросы среди прогнозов</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="72" t="inlineStr">
+        <is>
+          <t>Число брокеров</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="72" t="inlineStr">
+        <is>
+          <t>Чего нет в источниках</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="46" customHeight="1">
+      <c r="A19" s="72" t="inlineStr">
+        <is>
+          <t>Что проверить перед сдачей клиенту</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>